--- a/Datos 03.01 - L.xlsx
+++ b/Datos 03.01 - L.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Cursos\Introduccion a la Ciencia de Datos\GitHub\EP1053\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39BF3093-8E66-4D1B-82E4-CEB4142AE3D6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CASOS_10082020" sheetId="1" r:id="rId1"/>
-    <sheet name="POSITIVIDAD_10082020" sheetId="2" r:id="rId2"/>
+    <sheet name="CASOS_08022021" sheetId="1" r:id="rId1"/>
+    <sheet name="POSITIVIDAD_08022021" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="40">
   <si>
     <t>Pais</t>
   </si>
@@ -137,12 +138,15 @@
   </si>
   <si>
     <t>MINSA</t>
+  </si>
+  <si>
+    <t>PRUEBA ANTIGENO(+)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -976,26 +980,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1009,13 +1013,16 @@
         <v>3</v>
       </c>
       <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
         <v>4</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -1023,19 +1030,22 @@
         <v>7</v>
       </c>
       <c r="C5">
-        <v>78277</v>
+        <v>206585</v>
       </c>
       <c r="D5">
-        <v>146559</v>
+        <v>277989</v>
       </c>
       <c r="E5">
-        <v>224836</v>
+        <v>17177</v>
       </c>
       <c r="F5">
-        <v>9040</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>501751</v>
+      </c>
+      <c r="G5">
+        <v>16862</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1043,19 +1053,22 @@
         <v>8</v>
       </c>
       <c r="C6">
-        <v>5891</v>
+        <v>15499</v>
       </c>
       <c r="D6">
-        <v>17199</v>
+        <v>33696</v>
       </c>
       <c r="E6">
-        <v>23090</v>
+        <v>1865</v>
       </c>
       <c r="F6">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>51060</v>
+      </c>
+      <c r="G6">
+        <v>2226</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1063,19 +1076,22 @@
         <v>9</v>
       </c>
       <c r="C7">
-        <v>2860</v>
+        <v>6750</v>
       </c>
       <c r="D7">
-        <v>14809</v>
+        <v>33798</v>
       </c>
       <c r="E7">
-        <v>17669</v>
+        <v>826</v>
       </c>
       <c r="F7">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>41374</v>
+      </c>
+      <c r="G7">
+        <v>2683</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1083,19 +1099,22 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>3667</v>
+        <v>10987</v>
       </c>
       <c r="D8">
-        <v>16216</v>
+        <v>43235</v>
       </c>
       <c r="E8">
-        <v>19883</v>
+        <v>1395</v>
       </c>
       <c r="F8">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>55617</v>
+      </c>
+      <c r="G8">
+        <v>1844</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1103,19 +1122,22 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>307</v>
+        <v>1524</v>
       </c>
       <c r="D9">
-        <v>4438</v>
+        <v>16655</v>
       </c>
       <c r="E9">
-        <v>4745</v>
+        <v>380</v>
       </c>
       <c r="F9">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>18559</v>
+      </c>
+      <c r="G9">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -1123,19 +1145,22 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>3050</v>
+        <v>8936</v>
       </c>
       <c r="D10">
-        <v>3829</v>
+        <v>20401</v>
       </c>
       <c r="E10">
-        <v>6879</v>
+        <v>1237</v>
       </c>
       <c r="F10">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>30574</v>
+      </c>
+      <c r="G10">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -1143,19 +1168,22 @@
         <v>13</v>
       </c>
       <c r="C11">
-        <v>2108</v>
+        <v>6334</v>
       </c>
       <c r="D11">
-        <v>16767</v>
+        <v>29782</v>
       </c>
       <c r="E11">
-        <v>18875</v>
+        <v>312</v>
       </c>
       <c r="F11">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>36428</v>
+      </c>
+      <c r="G11">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -1163,19 +1191,22 @@
         <v>14</v>
       </c>
       <c r="C12">
-        <v>950</v>
+        <v>3629</v>
       </c>
       <c r="D12">
-        <v>21786</v>
+        <v>42337</v>
       </c>
       <c r="E12">
-        <v>22736</v>
+        <v>1375</v>
       </c>
       <c r="F12">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>47341</v>
+      </c>
+      <c r="G12">
+        <v>2339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -1183,19 +1214,22 @@
         <v>15</v>
       </c>
       <c r="C13">
-        <v>968</v>
+        <v>2535</v>
       </c>
       <c r="D13">
-        <v>6157</v>
+        <v>17228</v>
       </c>
       <c r="E13">
-        <v>7125</v>
+        <v>307</v>
       </c>
       <c r="F13">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>20070</v>
+      </c>
+      <c r="G13">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -1203,19 +1237,22 @@
         <v>16</v>
       </c>
       <c r="C14">
-        <v>2569</v>
+        <v>5855</v>
       </c>
       <c r="D14">
-        <v>12337</v>
+        <v>29452</v>
       </c>
       <c r="E14">
-        <v>14906</v>
+        <v>2215</v>
       </c>
       <c r="F14">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>37522</v>
+      </c>
+      <c r="G14">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -1223,19 +1260,22 @@
         <v>17</v>
       </c>
       <c r="C15">
-        <v>1667</v>
+        <v>5932</v>
       </c>
       <c r="D15">
-        <v>8056</v>
+        <v>30206</v>
       </c>
       <c r="E15">
-        <v>9723</v>
+        <v>1335</v>
       </c>
       <c r="F15">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>37473</v>
+      </c>
+      <c r="G15">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -1243,19 +1283,22 @@
         <v>18</v>
       </c>
       <c r="C16">
-        <v>2766</v>
+        <v>9694</v>
       </c>
       <c r="D16">
-        <v>11302</v>
+        <v>25431</v>
       </c>
       <c r="E16">
-        <v>14068</v>
+        <v>3923</v>
       </c>
       <c r="F16">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+        <v>39048</v>
+      </c>
+      <c r="G16">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -1263,19 +1306,22 @@
         <v>19</v>
       </c>
       <c r="C17">
-        <v>2070</v>
+        <v>5970</v>
       </c>
       <c r="D17">
-        <v>6546</v>
+        <v>23293</v>
       </c>
       <c r="E17">
-        <v>8616</v>
+        <v>460</v>
       </c>
       <c r="F17">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+        <v>29723</v>
+      </c>
+      <c r="G17">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -1283,19 +1329,22 @@
         <v>20</v>
       </c>
       <c r="C18">
-        <v>1048</v>
+        <v>3107</v>
       </c>
       <c r="D18">
-        <v>7142</v>
+        <v>19589</v>
       </c>
       <c r="E18">
-        <v>8190</v>
+        <v>1271</v>
       </c>
       <c r="F18">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23967</v>
+      </c>
+      <c r="G18">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -1303,19 +1352,22 @@
         <v>21</v>
       </c>
       <c r="C19">
-        <v>140</v>
+        <v>3068</v>
       </c>
       <c r="D19">
-        <v>1193</v>
+        <v>6583</v>
       </c>
       <c r="E19">
-        <v>1333</v>
+        <v>493</v>
       </c>
       <c r="F19">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10144</v>
+      </c>
+      <c r="G19">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -1323,19 +1375,22 @@
         <v>22</v>
       </c>
       <c r="C20">
-        <v>477</v>
+        <v>2564</v>
       </c>
       <c r="D20">
-        <v>3318</v>
+        <v>18996</v>
       </c>
       <c r="E20">
-        <v>3795</v>
+        <v>324</v>
       </c>
       <c r="F20">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21884</v>
+      </c>
+      <c r="G20">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -1343,19 +1398,22 @@
         <v>23</v>
       </c>
       <c r="C21">
-        <v>989</v>
+        <v>2826</v>
       </c>
       <c r="D21">
-        <v>3431</v>
+        <v>14361</v>
       </c>
       <c r="E21">
-        <v>4420</v>
+        <v>655</v>
       </c>
       <c r="F21">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17842</v>
+      </c>
+      <c r="G21">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -1363,19 +1421,22 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>3094</v>
+        <v>3766</v>
       </c>
       <c r="D22">
-        <v>9372</v>
+        <v>23666</v>
       </c>
       <c r="E22">
-        <v>12466</v>
+        <v>506</v>
       </c>
       <c r="F22">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+        <v>27938</v>
+      </c>
+      <c r="G22">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -1383,19 +1444,22 @@
         <v>25</v>
       </c>
       <c r="C23">
-        <v>2057</v>
+        <v>4561</v>
       </c>
       <c r="D23">
-        <v>8158</v>
+        <v>23460</v>
       </c>
       <c r="E23">
-        <v>10215</v>
+        <v>171</v>
       </c>
       <c r="F23">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28192</v>
+      </c>
+      <c r="G23">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -1403,19 +1467,22 @@
         <v>26</v>
       </c>
       <c r="C24">
-        <v>1650</v>
+        <v>3599</v>
       </c>
       <c r="D24">
-        <v>3383</v>
+        <v>13232</v>
       </c>
       <c r="E24">
-        <v>5033</v>
+        <v>687</v>
       </c>
       <c r="F24">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+        <v>17518</v>
+      </c>
+      <c r="G24">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -1423,19 +1490,22 @@
         <v>27</v>
       </c>
       <c r="C25">
-        <v>375</v>
+        <v>1393</v>
       </c>
       <c r="D25">
-        <v>2061</v>
+        <v>7136</v>
       </c>
       <c r="E25">
-        <v>2436</v>
+        <v>282</v>
       </c>
       <c r="F25">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8811</v>
+      </c>
+      <c r="G25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -1443,19 +1513,22 @@
         <v>28</v>
       </c>
       <c r="C26">
-        <v>176</v>
+        <v>591</v>
       </c>
       <c r="D26">
-        <v>2452</v>
+        <v>7432</v>
       </c>
       <c r="E26">
-        <v>2628</v>
+        <v>408</v>
       </c>
       <c r="F26">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8431</v>
+      </c>
+      <c r="G26">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -1463,19 +1536,22 @@
         <v>29</v>
       </c>
       <c r="C27">
-        <v>582</v>
+        <v>1722</v>
       </c>
       <c r="D27">
-        <v>4129</v>
+        <v>8692</v>
       </c>
       <c r="E27">
-        <v>4711</v>
+        <v>237</v>
       </c>
       <c r="F27">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+        <v>10651</v>
+      </c>
+      <c r="G27">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -1483,19 +1559,22 @@
         <v>30</v>
       </c>
       <c r="C28">
-        <v>935</v>
+        <v>1368</v>
       </c>
       <c r="D28">
-        <v>10058</v>
+        <v>20247</v>
       </c>
       <c r="E28">
-        <v>10993</v>
+        <v>241</v>
       </c>
       <c r="F28">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+        <v>21856</v>
+      </c>
+      <c r="G28">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -1503,19 +1582,22 @@
         <v>31</v>
       </c>
       <c r="C29">
-        <v>852</v>
+        <v>969</v>
       </c>
       <c r="D29">
-        <v>3226</v>
+        <v>8854</v>
       </c>
       <c r="E29">
-        <v>4078</v>
+        <v>14</v>
       </c>
       <c r="F29">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+        <v>9837</v>
+      </c>
+      <c r="G29">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -1523,16 +1605,19 @@
         <v>32</v>
       </c>
       <c r="C30">
-        <v>4890</v>
+        <v>8823</v>
       </c>
       <c r="D30">
-        <v>14794</v>
+        <v>27170</v>
       </c>
       <c r="E30">
-        <v>19684</v>
+        <v>1617</v>
       </c>
       <c r="F30">
-        <v>953</v>
+        <v>37610</v>
+      </c>
+      <c r="G30">
+        <v>1728</v>
       </c>
     </row>
   </sheetData>
@@ -1541,7 +1626,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1567,10 +1652,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1160384</v>
+        <v>3023137</v>
       </c>
       <c r="D2">
-        <v>224836</v>
+        <v>484574</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1581,10 +1666,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>92136</v>
+        <v>218793</v>
       </c>
       <c r="D3">
-        <v>23090</v>
+        <v>49195</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1595,10 +1680,10 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>98605</v>
+        <v>207188</v>
       </c>
       <c r="D4">
-        <v>17669</v>
+        <v>40548</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1609,10 +1694,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>147532</v>
+        <v>387908</v>
       </c>
       <c r="D5">
-        <v>19883</v>
+        <v>54222</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1623,10 +1708,10 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>45329</v>
+        <v>136034</v>
       </c>
       <c r="D6">
-        <v>4745</v>
+        <v>18179</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1637,10 +1722,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>58541</v>
+        <v>191278</v>
       </c>
       <c r="D7">
-        <v>6879</v>
+        <v>29337</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1651,10 +1736,10 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>79749</v>
+        <v>171575</v>
       </c>
       <c r="D8">
-        <v>18875</v>
+        <v>36116</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1665,10 +1750,10 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>90985</v>
+        <v>196609</v>
       </c>
       <c r="D9">
-        <v>22736</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1679,10 +1764,10 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>38430</v>
+        <v>90384</v>
       </c>
       <c r="D10">
-        <v>7125</v>
+        <v>19763</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1693,10 +1778,10 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>79740</v>
+        <v>169681</v>
       </c>
       <c r="D11">
-        <v>14906</v>
+        <v>35307</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1707,10 +1792,10 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>64445</v>
+        <v>213161</v>
       </c>
       <c r="D12">
-        <v>9723</v>
+        <v>36138</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1721,10 +1806,10 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>77959</v>
+        <v>204072</v>
       </c>
       <c r="D13">
-        <v>14068</v>
+        <v>35125</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1735,10 +1820,10 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>60335</v>
+        <v>170309</v>
       </c>
       <c r="D14">
-        <v>8616</v>
+        <v>29263</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1749,10 +1834,10 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>47344</v>
+        <v>122341</v>
       </c>
       <c r="D15">
-        <v>8190</v>
+        <v>22696</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1763,10 +1848,10 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>28853</v>
+        <v>100082</v>
       </c>
       <c r="D16">
-        <v>1333</v>
+        <v>9651</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1777,10 +1862,10 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>41812</v>
+        <v>120522</v>
       </c>
       <c r="D17">
-        <v>3795</v>
+        <v>21560</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1791,10 +1876,10 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>43385</v>
+        <v>110709</v>
       </c>
       <c r="D18">
-        <v>4420</v>
+        <v>17187</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1805,10 +1890,10 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>40863</v>
+        <v>83857</v>
       </c>
       <c r="D19">
-        <v>12466</v>
+        <v>27432</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1819,10 +1904,10 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>53801</v>
+        <v>117980</v>
       </c>
       <c r="D20">
-        <v>10215</v>
+        <v>28021</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1833,10 +1918,10 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>34044</v>
+        <v>91765</v>
       </c>
       <c r="D21">
-        <v>5033</v>
+        <v>16831</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1847,10 +1932,10 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>25312</v>
+        <v>67281</v>
       </c>
       <c r="D22">
-        <v>2436</v>
+        <v>8529</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1861,10 +1946,10 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>26028</v>
+        <v>65018</v>
       </c>
       <c r="D23">
-        <v>2628</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1875,10 +1960,10 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>21590</v>
+        <v>54619</v>
       </c>
       <c r="D24">
-        <v>4711</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1889,10 +1974,10 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>35481</v>
+        <v>75998</v>
       </c>
       <c r="D25">
-        <v>10993</v>
+        <v>21615</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1903,10 +1988,10 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24040</v>
+        <v>49625</v>
       </c>
       <c r="D26">
-        <v>4078</v>
+        <v>9823</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1917,10 +2002,10 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>73355</v>
+        <v>196207</v>
       </c>
       <c r="D27">
-        <v>19684</v>
+        <v>35993</v>
       </c>
     </row>
   </sheetData>
